--- a/stories/arbres/TREE-SAN-008.xlsx
+++ b/stories/arbres/TREE-SAN-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila est près de la fenêtre. Ses jambes ont envie de bouger. Papa dit : on va dehors. Maman prend les chaussures. On joue dehors, avec un adulte. Un moment. Puis on rentre.</t>
+          <t>Lila est près de la fenêtre. Ses jambes ont envie de bouger. On va dehors. Maman prend les chaussures. On joue dehors, avec un adulte. Un moment. Puis on rentre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est près de la fenêtre. Ses jambes ont envie de bouger.
+papa|On va dehors. Maman prend les chaussures. On joue dehors, avec un adulte.
+narrateur|Un moment. Puis on rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1513,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1682,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ils prennent le petit train, tout près. Papa tient la main. À la gare-jardin, ils descendent. Lila court sur l'herbe. Elle joue dehors, avec un adulte. Papa reste près d'elle. Maman arrive.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lila veut bouger. Où joue-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a bougé dehors. Un adulte était là. Le train attendra pour rentrer.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2231,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2211,7 +2260,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tom lance un ballon. Lila court. Ils jouent dehors. Papa, l'adulte, les voit. Maman dit : encore un moment.</t>
+          <t>Tom lance un ballon. Lila court. Ils jouent dehors. Papa, l'adulte, les voit. Encore un moment.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2349,6 +2398,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom lance un ballon. Lila court. Ils jouent dehors. Papa, l'adulte, les voit.
+maman|Encore un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2590,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2757,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, l'herbe est fraîche. Lila joue dehors, avec un adulte. Tom aussi. Puis le train.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2924,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3091,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila a de l'énergie. Elle joue dehors, avec un adulte. Tom lance.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3258,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3207,7 +3287,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le soir, le ciel est rose. Lila joue dehors, avec un adulte. Tom dit : on rentre.</t>
+          <t>Le soir, le ciel est rose. Lila joue dehors, avec un adulte. On rentre.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3345,6 +3425,12 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, le ciel est rose. Lila joue dehors, avec un adulte.
+enfant-m|On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa ramasse des feuilles. Lila l'aide. Elles jouent dehors, avec un adulte. Papa marche à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3951,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4118,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Léa et Lila jouent dehors, avec un adulte. Une feuille vole.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4285,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4452,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Léa chante.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4619,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4786,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, elles rangent. Lila a joué dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4953,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5120,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami suit un petit chemin. Lila aussi. Ils jouent dehors. Maman, l'adulte, est là. Le train sifflera plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5311,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5478,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Sami et Lila jouent dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5645,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5812,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Sami saute à cloche-pied.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5979,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6146,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, le train les reprend. Lila a joué dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6313,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6309,6 +6480,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Ils prennent le bus. Maman est à côté. Un adulte. Ils descendent au parc. Lila respire l'air. Elle joue dehors, avec un adulte. Papa les rejoint.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Après le bus, Lila joue où ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Le bus les a menées au parc. Lila joue dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6841,6 +7027,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7005,6 +7196,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a un cerceau. Lila le fait rouler. Ils jouent dehors. Maman, l'adulte, les voit.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7387,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7353,6 +7554,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, le cerceau roule. Lila joue dehors, avec un adulte. Tom rit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7721,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7888,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Tom souffle.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8055,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8222,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, le bus revient. Lila a joué dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8389,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8187,7 +8418,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Léa grimpe sur la petite butte. Lila aussi. Elles jouent dehors, avec un adulte. Papa dit : je vous vois.</t>
+          <t>Léa grimpe sur la petite butte. Lila aussi. Elles jouent dehors, avec un adulte. Je vous vois.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8325,6 +8556,12 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa grimpe sur la petite butte. Lila aussi. Elles jouent dehors, avec un adulte.
+papa|Je vous vois.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8748,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8915,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, la butte est douce. Lila joue dehors, avec un adulte. Léa aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9082,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9249,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Léa s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9416,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9321,6 +9583,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, elles redescendent. Lila a joué dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9750,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9917,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a une corde à sauter. Lila essaie. Ils jouent dehors. Un adulte compte. C'est maman.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10108,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9993,6 +10275,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, la corde tape. Lila joue dehors, avec un adulte. Sami compte.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10442,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10609,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Sami pose la corde.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10776,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10943,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, le bus les attend. Lila a joué dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11110,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10965,6 +11277,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Papa prend la voiture. Lila s'assoit. Maman aussi. Ils arrivent à la cour de la ferme. Lila court. Elle joue dehors, avec un adulte. L'air sent le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11458,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|À la ferme, Lila joue où ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11631,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|La voiture est rangée. Lila a bougé. Dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11497,6 +11824,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11661,6 +11993,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a un seau. Ils portent de l'herbe. Ils jouent dehors. Papa, l'adulte, marche avec eux.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11847,6 +12184,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12009,6 +12351,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, la cour est calme. Lila joue dehors, avec un adulte. Tom aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12171,6 +12518,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12333,6 +12685,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Tom pose le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12495,6 +12852,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12657,6 +13019,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, la voiture rentre. Lila a joué dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12819,6 +13186,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12981,6 +13353,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa écoute une poule, loin. Lila aussi. Elles jouent dehors, avec un adulte. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13167,6 +13544,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13329,6 +13711,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Léa et Lila jouent dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13491,6 +13878,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13653,6 +14045,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Léa bâille.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13815,6 +14212,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13977,6 +14379,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, elles saluent la poule. Lila a joué dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14139,6 +14546,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14301,6 +14713,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami marche sur une planche. Lila l'imite, tout doux. Ils jouent dehors. Un adulte les voit. C'est papa.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14487,6 +14904,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14649,6 +15071,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, la planche est sèche. Lila joue dehors, avec un adulte. Sami aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14811,6 +15238,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14973,6 +15405,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Sami s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15135,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15297,6 +15739,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, la voiture part. Lila a joué dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15459,6 +15906,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15477,7 +15929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15515,6 +15967,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-008.xlsx
+++ b/stories/arbres/TREE-SAN-008.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Un moment. Puis on rentre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1687,6 +1694,7 @@
           <t>narrateur|Ils prennent le petit train, tout près. Papa tient la main. À la gare-jardin, ils descendent. Lila court sur l'herbe. Elle joue dehors, avec un adulte. Papa reste près d'elle. Maman arrive.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1878,7 @@
           <t>narrateur|Lila veut bouger. Où joue-t-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
           <t>narrateur|Lila a bougé dehors. Un adulte était là. Le train attendra pour rentrer.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2236,6 +2246,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2404,6 +2415,7 @@
 maman|Encore un moment.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2595,6 +2607,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2762,6 +2775,7 @@
           <t>narrateur|Le matin, l'herbe est fraîche. Lila joue dehors, avec un adulte. Tom aussi. Puis le train.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2929,6 +2943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3096,6 +3111,7 @@
           <t>narrateur|Après la sieste, Lila a de l'énergie. Elle joue dehors, avec un adulte. Tom lance.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3263,6 +3279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3448,7 @@
 enfant-m|On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3784,7 @@
           <t>narrateur|Léa ramasse des feuilles. Lila l'aide. Elles jouent dehors, avec un adulte. Papa marche à côté.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3956,6 +3976,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4123,6 +4144,7 @@
           <t>narrateur|Le matin, Léa et Lila jouent dehors, avec un adulte. Une feuille vole.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4290,6 +4312,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4457,6 +4480,7 @@
           <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Léa chante.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4624,6 +4648,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4791,6 +4816,7 @@
           <t>narrateur|Le soir, elles rangent. Lila a joué dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4958,6 +4984,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5125,6 +5152,7 @@
           <t>narrateur|Sami suit un petit chemin. Lila aussi. Ils jouent dehors. Maman, l'adulte, est là. Le train sifflera plus tard.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5316,6 +5344,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5483,6 +5512,7 @@
           <t>narrateur|Le matin, Sami et Lila jouent dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5650,6 +5680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5817,6 +5848,7 @@
           <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Sami saute à cloche-pied.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5984,6 +6016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6151,6 +6184,7 @@
           <t>narrateur|Le soir, le train les reprend. Lila a joué dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6318,6 +6352,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6485,6 +6520,11 @@
           <t>narrateur|Ils prennent le bus. Maman est à côté. Un adulte. Ils descendent au parc. Lila respire l'air. Elle joue dehors, avec un adulte. Papa les rejoint.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6708,7 @@
           <t>narrateur|Après le bus, Lila joue où ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6880,11 @@
           <t>narrateur|Le bus les a menées au parc. Lila joue dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7034,6 +7080,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7201,6 +7248,7 @@
           <t>narrateur|Tom a un cerceau. Lila le fait rouler. Ils jouent dehors. Maman, l'adulte, les voit.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7392,6 +7440,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7559,6 +7608,7 @@
           <t>narrateur|Le matin, le cerceau roule. Lila joue dehors, avec un adulte. Tom rit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7726,6 +7776,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7893,6 +7944,7 @@
           <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Tom souffle.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8060,6 +8112,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8227,6 +8280,7 @@
           <t>narrateur|Le soir, le bus revient. Lila a joué dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8394,6 +8448,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8562,6 +8617,7 @@
 papa|Je vous vois.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8753,6 +8809,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8920,6 +8977,7 @@
           <t>narrateur|Le matin, la butte est douce. Lila joue dehors, avec un adulte. Léa aussi.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9087,6 +9145,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9254,6 +9313,7 @@
           <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Léa s'assoit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9421,6 +9481,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9588,6 +9649,7 @@
           <t>narrateur|Le soir, elles redescendent. Lila a joué dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9755,6 +9817,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9922,6 +9985,7 @@
           <t>narrateur|Sami a une corde à sauter. Lila essaie. Ils jouent dehors. Un adulte compte. C'est maman.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10113,6 +10177,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10280,6 +10345,7 @@
           <t>narrateur|Le matin, la corde tape. Lila joue dehors, avec un adulte. Sami compte.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10447,6 +10513,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10614,6 +10681,7 @@
           <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Sami pose la corde.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10781,6 +10849,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10948,6 +11017,7 @@
           <t>narrateur|Le soir, le bus les attend. Lila a joué dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11115,6 +11185,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11282,6 +11353,7 @@
           <t>narrateur|Papa prend la voiture. Lila s'assoit. Maman aussi. Ils arrivent à la cour de la ferme. Lila court. Elle joue dehors, avec un adulte. L'air sent le foin.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11465,6 +11537,7 @@
           <t>narrateur|À la ferme, Lila joue où ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11636,6 +11709,7 @@
           <t>narrateur|La voiture est rangée. Lila a bougé. Dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11831,6 +11905,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11998,6 +12073,7 @@
           <t>narrateur|Tom a un seau. Ils portent de l'herbe. Ils jouent dehors. Papa, l'adulte, marche avec eux.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12189,6 +12265,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12356,6 +12433,7 @@
           <t>narrateur|Le matin, la cour est calme. Lila joue dehors, avec un adulte. Tom aussi.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12523,6 +12601,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12690,6 +12769,7 @@
           <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Tom pose le seau.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12857,6 +12937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13024,6 +13105,7 @@
           <t>narrateur|Le soir, la voiture rentre. Lila a joué dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13191,6 +13273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13358,6 +13441,7 @@
           <t>narrateur|Léa écoute une poule, loin. Lila aussi. Elles jouent dehors, avec un adulte. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13549,6 +13633,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13716,6 +13801,7 @@
           <t>narrateur|Le matin, Léa et Lila jouent dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13883,6 +13969,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14050,6 +14137,7 @@
           <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Léa bâille.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14217,6 +14305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14384,6 +14473,7 @@
           <t>narrateur|Le soir, elles saluent la poule. Lila a joué dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14551,6 +14641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14718,6 +14809,7 @@
           <t>narrateur|Sami marche sur une planche. Lila l'imite, tout doux. Ils jouent dehors. Un adulte les voit. C'est papa.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14909,6 +15001,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15076,6 +15169,7 @@
           <t>narrateur|Le matin, la planche est sèche. Lila joue dehors, avec un adulte. Sami aussi.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15243,6 +15337,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15410,6 +15505,7 @@
           <t>narrateur|Après la sieste, Lila joue dehors, avec un adulte. Sami s'assoit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15577,6 +15673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15744,6 +15841,7 @@
           <t>narrateur|Le soir, la voiture part. Lila a joué dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15911,6 +16009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15929,7 +16028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15974,6 +16073,20 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15988,7 +16101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16175,6 +16288,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
